--- a/branch/SXAU/resources/others/money.xlsx
+++ b/branch/SXAU/resources/others/money.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\HTML\github\branch\SXAU\resources\others\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\HTML\github\branch\SXAU\resources\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1178FF-DFCD-43F7-857C-E20E81FAB08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79928EFE-AE67-494F-9889-736C3949C1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{335928DB-CFAC-4ACE-B54E-2C90BF1ACF53}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{335928DB-CFAC-4ACE-B54E-2C90BF1ACF53}"/>
   </bookViews>
   <sheets>
     <sheet name="2024-2025-1" sheetId="1" r:id="rId1"/>
     <sheet name="2024-2025-2" sheetId="2" r:id="rId2"/>
+    <sheet name="2025-2026-1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="65">
   <si>
     <t>序号</t>
   </si>
@@ -242,6 +243,34 @@
   </si>
   <si>
     <t>心理科教具（打印）</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>排球赛饮水水</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>体测肺活量吹嘴</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>支出</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发生对象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>王桂</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
@@ -249,12 +278,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="184" formatCode="[$CNY]\ #,##0.00;[$CNY]\ \-#,##0.00"/>
+    <numFmt numFmtId="186" formatCode="yyyy\-m\-d\ h:mm;@"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -474,8 +505,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="华文行楷"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -655,8 +694,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -823,6 +874,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -950,7 +1074,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -996,6 +1120,81 @@
     </xf>
     <xf numFmtId="177" fontId="26" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="28" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="28" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1042,7 +1241,207 @@
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <name val="华文行楷"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1053,6 +1452,36 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{141BB789-828C-4A23-99A8-59D44CB6F884}" name="表4" displayName="表4" ref="A1:H4" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0" tableBorderDxfId="9">
+  <autoFilter ref="A1:H4" xr:uid="{141BB789-828C-4A23-99A8-59D44CB6F884}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{16035545-1C69-4219-82A9-0648E19397F1}" name="序号" dataDxfId="8">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{FC66BDD6-0D04-49EF-9996-2F276A666D14}" name="日期" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{1BE36DE7-0D82-45B7-A4A7-881BD941FAEA}" name="类型" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{6C85CCF3-A9EE-41FA-9184-B9F9701AF9F2}" name="发生对象" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1542900C-27B2-499E-9A83-77666734DC0A}" name="事件" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{458D236A-FA34-4828-B13F-6756938C931F}" name="金额" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{9FC428BD-E1CD-4E02-9788-1105169CCDC5}" name="结余" dataDxfId="2">
+      <calculatedColumnFormula>G1+'2025-2026-1'!$F2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{683D0BF4-8D9D-4EAF-9E80-9DD898F56DDF}" name="备注" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1420,7 +1849,7 @@
       <c r="H2" s="9"/>
       <c r="I2" s="15">
         <f ca="1">NOW()</f>
-        <v>45770.964346990739</v>
+        <v>45941.879959375001</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,7 +2352,7 @@
     <col min="3" max="3" width="13.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="37.44140625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.77734375" style="14" customWidth="1"/>
+    <col min="6" max="7" width="17.88671875" style="40" customWidth="1"/>
     <col min="8" max="8" width="11" style="2" customWidth="1"/>
     <col min="9" max="9" width="31.6640625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="1"/>
@@ -1945,10 +2374,10 @@
       <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="38" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
@@ -1969,21 +2398,21 @@
         <v>39</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="39">
         <v>142.39000000000004</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="39">
         <v>142.39000000000004</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="15">
+      <c r="I2" s="16">
         <f ca="1">NOW()</f>
-        <v>45770.964346990739</v>
+        <v>45941.879959375001</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2002,15 +2431,15 @@
       <c r="E3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="39">
         <v>-60</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="39">
         <f>G2+F3</f>
         <v>82.390000000000043</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="15"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -2028,15 +2457,15 @@
       <c r="E4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="39">
         <v>-78</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="39">
         <f>G3+F4</f>
         <v>4.3900000000000432</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="15"/>
+      <c r="I4" s="17"/>
     </row>
     <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -2054,15 +2483,15 @@
       <c r="E5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="39">
         <v>390</v>
       </c>
-      <c r="G5" s="13">
-        <f t="shared" ref="G5:G11" si="0">G4+F5</f>
+      <c r="G5" s="39">
+        <f t="shared" ref="G5:G12" si="0">G4+F5</f>
         <v>394.39000000000004</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="15"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2080,10 +2509,10 @@
       <c r="E6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="39">
         <v>-14</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="39">
         <f t="shared" si="0"/>
         <v>380.39000000000004</v>
       </c>
@@ -2105,10 +2534,10 @@
       <c r="E7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="39">
         <v>-27.2</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="39">
         <f t="shared" si="0"/>
         <v>353.19000000000005</v>
       </c>
@@ -2130,10 +2559,10 @@
       <c r="E8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="39">
         <v>-0.2</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="39">
         <f t="shared" si="0"/>
         <v>352.99000000000007</v>
       </c>
@@ -2155,10 +2584,10 @@
       <c r="E9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="39">
         <v>-0.2</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="39">
         <f t="shared" si="0"/>
         <v>352.79000000000008</v>
       </c>
@@ -2180,10 +2609,10 @@
       <c r="E10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="39">
         <v>-7</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="39">
         <f t="shared" si="0"/>
         <v>345.79000000000008</v>
       </c>
@@ -2205,10 +2634,10 @@
       <c r="E11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="39">
         <v>-0.6</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="39">
         <f t="shared" si="0"/>
         <v>345.19000000000005</v>
       </c>
@@ -2218,36 +2647,75 @@
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="B12" s="8">
+        <v>45803</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="39">
+        <v>-9.9</v>
+      </c>
+      <c r="G12" s="39">
+        <f t="shared" si="0"/>
+        <v>335.29000000000008</v>
+      </c>
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="B13" s="8">
+        <v>45805</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="39">
+        <v>-9.9</v>
+      </c>
+      <c r="G13" s="39">
+        <f t="shared" ref="G13" si="1">G12+F13</f>
+        <v>325.3900000000001</v>
+      </c>
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="B14" s="8">
+        <v>45814</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="39">
+        <v>-9.9</v>
+      </c>
+      <c r="G14" s="39">
+        <f t="shared" ref="G14:G15" si="2">G13+F14</f>
+        <v>315.49000000000012</v>
+      </c>
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2258,8 +2726,8 @@
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2270,8 +2738,8 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2282,8 +2750,8 @@
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2294,8 +2762,8 @@
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2306,8 +2774,8 @@
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2318,8 +2786,8 @@
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
       <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2330,8 +2798,8 @@
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
       <c r="H21" s="9"/>
     </row>
   </sheetData>
@@ -2349,4 +2817,151 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A7766B-1BF9-418D-8C50-4F6C9C59AF96}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A2" s="24">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="25">
+        <v>45941</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="27">
+        <v>315.49</v>
+      </c>
+      <c r="G2" s="27">
+        <v>315.49</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="28">
+        <f t="shared" ref="I2:I3" ca="1" si="0">NOW()</f>
+        <v>45941.879959375001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A3" s="33">
+        <f>ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="34">
+        <v>45941</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="36">
+        <v>8</v>
+      </c>
+      <c r="G3" s="36">
+        <f>G2+'2025-2026-1'!$F3</f>
+        <v>323.49</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="I3" s="29"/>
+    </row>
+    <row r="4" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
+        <f>ROW()-1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>45941</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="22">
+        <v>-20</v>
+      </c>
+      <c r="G4" s="22">
+        <f>G3+'2025-2026-1'!$F4</f>
+        <v>303.49</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="29"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I2:I5"/>
+  </mergeCells>
+  <phoneticPr fontId="27" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{EDF1018E-2AA4-4F7F-8AB1-6A9003E2CDFC}">
+      <formula1>"收入,支出,学期转结"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/branch/SXAU/resources/others/money.xlsx
+++ b/branch/SXAU/resources/others/money.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\HTML\github\branch\SXAU\resources\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79928EFE-AE67-494F-9889-736C3949C1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9A29E2-1A0C-4ABB-9E29-B5E938917861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{335928DB-CFAC-4ACE-B54E-2C90BF1ACF53}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="2025-2026-1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <webPublishing allowPng="1" targetScreenSize="1024x768" codePage="65001"/>
 </workbook>
 </file>
 
@@ -282,8 +283,8 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="184" formatCode="[$CNY]\ #,##0.00;[$CNY]\ \-#,##0.00"/>
-    <numFmt numFmtId="186" formatCode="yyyy\-m\-d\ h:mm;@"/>
+    <numFmt numFmtId="179" formatCode="[$CNY]\ #,##0.00;[$CNY]\ \-#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-m\-d\ h:mm;@"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -696,18 +697,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="1"/>
         <bgColor theme="4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -916,37 +917,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1074,7 +1044,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1118,6 +1088,30 @@
     <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="26" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1130,70 +1124,34 @@
     <xf numFmtId="177" fontId="26" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="28" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="28" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="21" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="25" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1315,6 +1273,8 @@
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1326,12 +1286,21 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1343,12 +1312,21 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1360,6 +1338,13 @@
         <charset val="134"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1424,22 +1409,12 @@
         <scheme val="none"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1455,32 +1430,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{141BB789-828C-4A23-99A8-59D44CB6F884}" name="表4" displayName="表4" ref="A1:H4" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0" tableBorderDxfId="9">
-  <autoFilter ref="A1:H4" xr:uid="{141BB789-828C-4A23-99A8-59D44CB6F884}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E084B574-35AD-4BD9-862B-E83984FED920}" name="表2" displayName="表2" ref="A1:H5" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0" tableBorderDxfId="9">
+  <autoFilter ref="A1:H5" xr:uid="{E084B574-35AD-4BD9-862B-E83984FED920}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{16035545-1C69-4219-82A9-0648E19397F1}" name="序号" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{4AD8EDB0-7368-440F-B6C3-23C4D0F47F9F}" name="序号" dataDxfId="8">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{FC66BDD6-0D04-49EF-9996-2F276A666D14}" name="日期" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{1BE36DE7-0D82-45B7-A4A7-881BD941FAEA}" name="类型" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{6C85CCF3-A9EE-41FA-9184-B9F9701AF9F2}" name="发生对象" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{1542900C-27B2-499E-9A83-77666734DC0A}" name="事件" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{458D236A-FA34-4828-B13F-6756938C931F}" name="金额" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{9FC428BD-E1CD-4E02-9788-1105169CCDC5}" name="结余" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{BC4AFA26-FD32-4120-B116-D75AA7A632FB}" name="日期" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{C4D66F14-A3C5-4933-927A-EFB02619A59D}" name="类型" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{D536483F-6102-4F76-9BEC-103E06C98A25}" name="发生对象" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{14727EB5-A405-418E-BBA2-C4780FD7E00C}" name="事件" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{A3FEB711-A277-44F8-8A3B-F16C35F6055F}" name="金额" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{97A21383-B9EA-4DC1-9342-09B71647E871}" name="结余" dataDxfId="2">
       <calculatedColumnFormula>G1+'2025-2026-1'!$F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{683D0BF4-8D9D-4EAF-9E80-9DD898F56DDF}" name="备注" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{011FAED9-E964-4750-808E-3DA19398E170}" name="备注" dataDxfId="1"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1847,9 +1813,9 @@
         <v>195</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="15">
+      <c r="I2" s="23">
         <f ca="1">NOW()</f>
-        <v>45941.879959375001</v>
+        <v>45941.891691435187</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1876,7 +1842,7 @@
         <v>159.19999999999999</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="15"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -1902,7 +1868,7 @@
         <v>153.19999999999999</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="15"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -1928,7 +1894,7 @@
         <v>141.5</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="15"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2352,7 +2318,7 @@
     <col min="3" max="3" width="13.109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="37.44140625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="17.88671875" style="40" customWidth="1"/>
+    <col min="6" max="7" width="17.88671875" style="22" customWidth="1"/>
     <col min="8" max="8" width="11" style="2" customWidth="1"/>
     <col min="9" max="9" width="31.6640625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="1"/>
@@ -2374,10 +2340,10 @@
       <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="20" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
@@ -2403,16 +2369,16 @@
       <c r="E2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="39">
+      <c r="F2" s="21">
         <v>142.39000000000004</v>
       </c>
-      <c r="G2" s="39">
+      <c r="G2" s="21">
         <v>142.39000000000004</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="16">
+      <c r="I2" s="24">
         <f ca="1">NOW()</f>
-        <v>45941.879959375001</v>
+        <v>45941.891691435187</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2431,15 +2397,15 @@
       <c r="E3" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="21">
         <v>-60</v>
       </c>
-      <c r="G3" s="39">
+      <c r="G3" s="21">
         <f>G2+F3</f>
         <v>82.390000000000043</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="17"/>
+      <c r="I3" s="25"/>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -2457,15 +2423,15 @@
       <c r="E4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="21">
         <v>-78</v>
       </c>
-      <c r="G4" s="39">
+      <c r="G4" s="21">
         <f>G3+F4</f>
         <v>4.3900000000000432</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="17"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -2483,15 +2449,15 @@
       <c r="E5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="21">
         <v>390</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="21">
         <f t="shared" ref="G5:G12" si="0">G4+F5</f>
         <v>394.39000000000004</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="18"/>
+      <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2509,10 +2475,10 @@
       <c r="E6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="21">
         <v>-14</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="21">
         <f t="shared" si="0"/>
         <v>380.39000000000004</v>
       </c>
@@ -2534,10 +2500,10 @@
       <c r="E7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="21">
         <v>-27.2</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="21">
         <f t="shared" si="0"/>
         <v>353.19000000000005</v>
       </c>
@@ -2559,10 +2525,10 @@
       <c r="E8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="21">
         <v>-0.2</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="21">
         <f t="shared" si="0"/>
         <v>352.99000000000007</v>
       </c>
@@ -2584,10 +2550,10 @@
       <c r="E9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="21">
         <v>-0.2</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="21">
         <f t="shared" si="0"/>
         <v>352.79000000000008</v>
       </c>
@@ -2609,10 +2575,10 @@
       <c r="E10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="21">
         <v>-7</v>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="21">
         <f t="shared" si="0"/>
         <v>345.79000000000008</v>
       </c>
@@ -2634,10 +2600,10 @@
       <c r="E11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="21">
         <v>-0.6</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="21">
         <f t="shared" si="0"/>
         <v>345.19000000000005</v>
       </c>
@@ -2659,10 +2625,10 @@
       <c r="E12" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="21">
         <v>-9.9</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="21">
         <f t="shared" si="0"/>
         <v>335.29000000000008</v>
       </c>
@@ -2684,10 +2650,10 @@
       <c r="E13" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="21">
         <v>-9.9</v>
       </c>
-      <c r="G13" s="39">
+      <c r="G13" s="21">
         <f t="shared" ref="G13" si="1">G12+F13</f>
         <v>325.3900000000001</v>
       </c>
@@ -2709,11 +2675,11 @@
       <c r="E14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="21">
         <v>-9.9</v>
       </c>
-      <c r="G14" s="39">
-        <f t="shared" ref="G14:G15" si="2">G13+F14</f>
+      <c r="G14" s="21">
+        <f t="shared" ref="G14" si="2">G13+F14</f>
         <v>315.49000000000012</v>
       </c>
       <c r="H14" s="9"/>
@@ -2726,8 +2692,8 @@
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2738,8 +2704,8 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2750,8 +2716,8 @@
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2762,8 +2728,8 @@
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2774,8 +2740,8 @@
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2786,8 +2752,8 @@
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
       <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2798,8 +2764,8 @@
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
       <c r="H21" s="9"/>
     </row>
   </sheetData>
@@ -2825,129 +2791,143 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="22" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.33203125" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="26.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="34" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A2" s="24">
+      <c r="A2" s="30">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="31">
         <v>45941</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="32">
         <v>315.49</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="32">
         <v>315.49</v>
       </c>
-      <c r="H2" s="26"/>
-      <c r="I2" s="28">
-        <f t="shared" ref="I2:I3" ca="1" si="0">NOW()</f>
-        <v>45941.879959375001</v>
+      <c r="H2" s="30"/>
+      <c r="I2" s="35">
+        <f t="shared" ref="I2" ca="1" si="0">NOW()</f>
+        <v>45941.891691435187</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="33">
+      <c r="A3" s="30">
         <f>ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="31">
         <v>45941</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="36">
+      <c r="F3" s="32">
         <v>8</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="32">
         <f>G2+'2025-2026-1'!$F3</f>
         <v>323.49</v>
       </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="29"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A4" s="21">
+      <c r="A4" s="30">
         <f>ROW()-1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="31">
         <v>45941</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="32">
         <v>-20</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="32">
         <f>G3+'2025-2026-1'!$F4</f>
         <v>303.49</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="29"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I5" s="29"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="36"/>
+    </row>
+    <row r="5" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <f>ROW()-1</f>
+        <v>4</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18">
+        <f>G4+'2025-2026-1'!$F5</f>
+        <v>303.49</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/branch/SXAU/resources/others/money.xlsx
+++ b/branch/SXAU/resources/others/money.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python\HTML\github\branch\SXAU\resources\others\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9A29E2-1A0C-4ABB-9E29-B5E938917861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13D5168-DF9F-4CDE-9969-927A19AFDB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{335928DB-CFAC-4ACE-B54E-2C90BF1ACF53}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{335928DB-CFAC-4ACE-B54E-2C90BF1ACF53}"/>
   </bookViews>
   <sheets>
     <sheet name="2024-2025-1" sheetId="1" r:id="rId1"/>
     <sheet name="2024-2025-2" sheetId="2" r:id="rId2"/>
     <sheet name="2025-2026-1" sheetId="3" r:id="rId3"/>
+    <sheet name="2025-2026-2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <webPublishing allowPng="1" targetScreenSize="1024x768" codePage="65001"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="69">
   <si>
     <t>序号</t>
   </si>
@@ -272,6 +273,22 @@
   </si>
   <si>
     <t>王桂</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>优秀团员投票表</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>发展对象投票</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>杨喆雅</t>
+    <phoneticPr fontId="27" type="noConversion"/>
+  </si>
+  <si>
+    <t>去向表打印(共4次)</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
 </sst>
@@ -1044,7 +1061,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1112,6 +1129,24 @@
     <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="26" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1124,34 +1159,7 @@
     <xf numFmtId="177" fontId="26" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="21" fillId="34" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="21" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1199,24 +1207,7 @@
     <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="楷体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -1392,6 +1383,239 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="0"/>
+        <name val="华文行楷"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF8EA9DB"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <name val="楷体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -1430,21 +1654,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E084B574-35AD-4BD9-862B-E83984FED920}" name="表2" displayName="表2" ref="A1:H5" totalsRowShown="0" headerRowDxfId="10" dataDxfId="0" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E084B574-35AD-4BD9-862B-E83984FED920}" name="表2" displayName="表2" ref="A1:H5" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:H5" xr:uid="{E084B574-35AD-4BD9-862B-E83984FED920}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4AD8EDB0-7368-440F-B6C3-23C4D0F47F9F}" name="序号" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{4AD8EDB0-7368-440F-B6C3-23C4D0F47F9F}" name="序号" dataDxfId="7">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{BC4AFA26-FD32-4120-B116-D75AA7A632FB}" name="日期" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C4D66F14-A3C5-4933-927A-EFB02619A59D}" name="类型" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{D536483F-6102-4F76-9BEC-103E06C98A25}" name="发生对象" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{14727EB5-A405-418E-BBA2-C4780FD7E00C}" name="事件" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{A3FEB711-A277-44F8-8A3B-F16C35F6055F}" name="金额" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{97A21383-B9EA-4DC1-9342-09B71647E871}" name="结余" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{BC4AFA26-FD32-4120-B116-D75AA7A632FB}" name="日期" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{C4D66F14-A3C5-4933-927A-EFB02619A59D}" name="类型" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{D536483F-6102-4F76-9BEC-103E06C98A25}" name="发生对象" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{14727EB5-A405-418E-BBA2-C4780FD7E00C}" name="事件" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{A3FEB711-A277-44F8-8A3B-F16C35F6055F}" name="金额" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{97A21383-B9EA-4DC1-9342-09B71647E871}" name="结余" dataDxfId="1">
       <calculatedColumnFormula>G1+'2025-2026-1'!$F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{011FAED9-E964-4750-808E-3DA19398E170}" name="备注" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{011FAED9-E964-4750-808E-3DA19398E170}" name="备注" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E84B5D3-C93A-49CF-B1E7-A10F19FBB93C}" name="表2_2" displayName="表2_2" ref="A1:H5" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" tableBorderDxfId="19">
+  <autoFilter ref="A1:H5" xr:uid="{E084B574-35AD-4BD9-862B-E83984FED920}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{BB069A57-06CB-40E6-BB69-D421FD476573}" name="序号" dataDxfId="18">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{C00483E8-07CC-4B12-AACB-CCD178CE6804}" name="日期" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{F489644F-6E70-4FB9-AFDA-113942E87D83}" name="类型" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{F9A5E8B2-7DDF-4274-A653-E34475F10543}" name="发生对象" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{FDF4CC0E-95ED-4F78-8A1C-0284D981AB86}" name="事件" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{C3BC0B6F-CEF3-493A-AB93-1D4E097D1D58}" name="金额" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{DC904FB9-EB76-45F1-9CE6-10B163A50255}" name="结余" dataDxfId="12">
+      <calculatedColumnFormula>G1+'2025-2026-2'!$F2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{63A62FD6-1C8B-4D8B-88B7-8135C73EBB8F}" name="备注" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1813,9 +2058,9 @@
         <v>195</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="23">
+      <c r="I2" s="29">
         <f ca="1">NOW()</f>
-        <v>45941.891691435187</v>
+        <v>46206.846764930553</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -1842,7 +2087,7 @@
         <v>159.19999999999999</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="23"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -1868,7 +2113,7 @@
         <v>153.19999999999999</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="23"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -1894,7 +2139,7 @@
         <v>141.5</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="23"/>
+      <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2376,9 +2621,9 @@
         <v>142.39000000000004</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="24">
+      <c r="I2" s="30">
         <f ca="1">NOW()</f>
-        <v>45941.891691435187</v>
+        <v>46206.846764930553</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2405,7 +2650,7 @@
         <v>82.390000000000043</v>
       </c>
       <c r="H3" s="9"/>
-      <c r="I3" s="25"/>
+      <c r="I3" s="31"/>
     </row>
     <row r="4" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
@@ -2431,7 +2676,7 @@
         <v>4.3900000000000432</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
@@ -2457,7 +2702,7 @@
         <v>394.39000000000004</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="I5" s="32"/>
     </row>
     <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
@@ -2801,133 +3046,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A2" s="30">
+      <c r="A2" s="17">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2" s="3">
         <v>45941</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="32">
+      <c r="F2" s="18">
         <v>315.49</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="18">
         <v>315.49</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="35">
+      <c r="H2" s="17"/>
+      <c r="I2" s="27">
         <f t="shared" ref="I2" ca="1" si="0">NOW()</f>
-        <v>45941.891691435187</v>
+        <v>46206.846764930553</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A3" s="30">
+      <c r="A3" s="17">
         <f>ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="3">
         <v>45941</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="18">
         <v>8</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="18">
         <f>G2+'2025-2026-1'!$F3</f>
         <v>323.49</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="36"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="28"/>
     </row>
     <row r="4" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
+      <c r="A4" s="17">
         <f>ROW()-1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="3">
         <v>45941</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="18">
         <v>-20</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="18">
         <f>G3+'2025-2026-1'!$F4</f>
         <v>303.49</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="36"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="28"/>
     </row>
     <row r="5" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
-        <f>ROW()-1</f>
-        <v>4</v>
-      </c>
+      <c r="A5" s="17"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="18">
-        <f>G4+'2025-2026-1'!$F5</f>
-        <v>303.49</v>
-      </c>
+      <c r="G5" s="18"/>
       <c r="H5" s="17"/>
-      <c r="I5" s="36"/>
+      <c r="I5" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2944,4 +3183,174 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3101C1E6-3FC4-43AA-ACC8-569F57262A0D}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22" style="1" customWidth="1"/>
+    <col min="6" max="7" width="15.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="21.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45941</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="18">
+        <v>303.49</v>
+      </c>
+      <c r="G2" s="18">
+        <v>303.49</v>
+      </c>
+      <c r="H2" s="17"/>
+      <c r="I2" s="27">
+        <f t="shared" ref="I2" ca="1" si="0">NOW()</f>
+        <v>46206.846764930553</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <f>ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46097</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="18">
+        <v>-8</v>
+      </c>
+      <c r="G3" s="18">
+        <f>G2+表2_2[[#This Row],[金额]]</f>
+        <v>295.49</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="28"/>
+    </row>
+    <row r="4" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <f>ROW()-1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="18">
+        <v>-8</v>
+      </c>
+      <c r="G4" s="18">
+        <f>G3+'2025-2026-2'!$F4</f>
+        <v>287.49</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="28"/>
+    </row>
+    <row r="5" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46190</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="18">
+        <v>-1.4</v>
+      </c>
+      <c r="G5" s="18">
+        <f>G4+'2025-2026-2'!$F5</f>
+        <v>286.09000000000003</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I2:I5"/>
+  </mergeCells>
+  <phoneticPr fontId="27" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{087E1567-42C1-4020-BC89-DF36C0546FC3}">
+      <formula1>"收入,支出,学期转结"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>